--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>41323</v>
@@ -23987,7 +23987,7 @@
         <v>2554</v>
       </c>
       <c r="K56" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57">
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45248,16 +45248,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>527177</v>
+        <v>527164</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-0.003783218910803339</v>
+        <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>
@@ -45275,7 +45275,7 @@
         <v>43419</v>
       </c>
       <c r="K56" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57">
@@ -45291,7 +45291,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.1654017531113838</v>
+        <v>-0.1653811717036824</v>
       </c>
       <c r="E57" t="n">
         <v>13</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>41323</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -3386,10 +3386,10 @@
         <v>0.01819581627671161</v>
       </c>
       <c r="J56" t="n">
-        <v>13934</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>107</v>
+        <v>13998</v>
       </c>
     </row>
     <row r="57">
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>41323</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3386,10 +3386,10 @@
         <v>0.01819581627671161</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>7691</v>
       </c>
       <c r="K56" t="n">
-        <v>13998</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>41323</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -3386,10 +3386,10 @@
         <v>0.01819581627671161</v>
       </c>
       <c r="J56" t="n">
-        <v>7691</v>
+        <v>14045</v>
       </c>
       <c r="K56" t="n">
-        <v>6355</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>41323</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>
@@ -45272,10 +45272,10 @@
         <v>0.1413611559910982</v>
       </c>
       <c r="J56" t="n">
-        <v>43419</v>
+        <v>43488</v>
       </c>
       <c r="K56" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3389,7 +3389,7 @@
         <v>14045</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -34631,7 +34631,7 @@
         <v>1648</v>
       </c>
       <c r="K56" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57">
@@ -45275,7 +45275,7 @@
         <v>43488</v>
       </c>
       <c r="K56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -3389,7 +3389,7 @@
         <v>14045</v>
       </c>
       <c r="K56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -6937,7 +6937,7 @@
         <v>1817</v>
       </c>
       <c r="K56" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57">
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -20439,7 +20439,7 @@
         <v>3617</v>
       </c>
       <c r="K56" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57">
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>41323</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -34631,7 +34631,7 @@
         <v>1648</v>
       </c>
       <c r="K56" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57">
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>
@@ -45275,7 +45275,7 @@
         <v>43488</v>
       </c>
       <c r="K56" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>41323</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>
@@ -45275,7 +45275,7 @@
         <v>43488</v>
       </c>
       <c r="K56" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -20439,7 +20439,7 @@
         <v>3617</v>
       </c>
       <c r="K56" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57">
@@ -34631,7 +34631,7 @@
         <v>1648</v>
       </c>
       <c r="K56" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57">
@@ -45275,7 +45275,7 @@
         <v>43488</v>
       </c>
       <c r="K56" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -31083,7 +31083,7 @@
         <v>4461</v>
       </c>
       <c r="K56" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57">
@@ -34631,7 +34631,7 @@
         <v>1648</v>
       </c>
       <c r="K56" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57">
@@ -38179,7 +38179,7 @@
         <v>3620</v>
       </c>
       <c r="K56" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57">
@@ -45275,7 +45275,7 @@
         <v>43488</v>
       </c>
       <c r="K56" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -3389,7 +3389,7 @@
         <v>14045</v>
       </c>
       <c r="K56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>41323</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -31083,7 +31083,7 @@
         <v>4461</v>
       </c>
       <c r="K56" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57">
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>
@@ -45275,7 +45275,7 @@
         <v>43488</v>
       </c>
       <c r="K56" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -3389,7 +3389,7 @@
         <v>14045</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -20439,7 +20439,7 @@
         <v>3617</v>
       </c>
       <c r="K56" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57">
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>41323</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -41727,7 +41727,7 @@
         <v>2918</v>
       </c>
       <c r="K56" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57">
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>
@@ -45275,7 +45275,7 @@
         <v>43488</v>
       </c>
       <c r="K56" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>41323</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -3380,16 +3380,16 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>6501</v>
+        <v>6729</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.01819581627671161</v>
+        <v>0.01962293912194389</v>
       </c>
       <c r="J56" t="n">
         <v>14045</v>
       </c>
       <c r="K56" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.7220982485906965</v>
+        <v>-0.7224872158480512</v>
       </c>
       <c r="J57" t="n">
         <v>10120</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -20439,7 +20439,7 @@
         <v>3617</v>
       </c>
       <c r="K56" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57">
@@ -23969,19 +23969,19 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
-        <v>41323</v>
+        <v>35588</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>4653</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>-0.02618396534617526</v>
       </c>
       <c r="J56" t="n">
         <v>2554</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -31083,7 +31083,7 @@
         <v>4461</v>
       </c>
       <c r="K56" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57">
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -41718,16 +41718,16 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>330</v>
+        <v>416</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>0.001783307413167444</v>
       </c>
       <c r="J56" t="n">
         <v>2918</v>
       </c>
       <c r="K56" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57">
@@ -41758,7 +41758,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.2644893727319855</v>
+        <v>-0.265798679389787</v>
       </c>
       <c r="J57" t="n">
         <v>1120</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>
@@ -45266,16 +45266,16 @@
         <v>26590</v>
       </c>
       <c r="H56" t="n">
-        <v>58303</v>
+        <v>57091</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1413611559910982</v>
+        <v>0.1384514924029452</v>
       </c>
       <c r="J56" t="n">
         <v>43488</v>
       </c>
       <c r="K56" t="n">
-        <v>112</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57">
@@ -45306,7 +45306,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.554689899164118</v>
+        <v>-0.5535517719848001</v>
       </c>
       <c r="J57" t="n">
         <v>29799</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>35588</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>35588</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3371,7 +3371,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>156168</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>37421</v>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>35588</v>
@@ -27517,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -31065,7 +31065,7 @@
         <v>0.03328385476136104</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>52024</v>
@@ -34613,7 +34613,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>30655</v>
@@ -38161,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -41709,7 +41709,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>47895</v>
@@ -45257,7 +45257,7 @@
         <v>-0.003807785267366997</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>390533</v>
@@ -45272,7 +45272,7 @@
         <v>0.1384514924029452</v>
       </c>
       <c r="J56" t="n">
-        <v>43488</v>
+        <v>43532</v>
       </c>
       <c r="K56" t="n">
         <v>181</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -45997,7 +45997,7 @@
         <v>-0.004148405621883029</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -45997,7 +45997,7 @@
         <v>-0.004148405621883029</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -3685,7 +3685,7 @@
         <v>14045</v>
       </c>
       <c r="K64" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65">
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -35260,7 +35260,7 @@
         <v>1648</v>
       </c>
       <c r="K64" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65">
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -45997,7 +45997,7 @@
         <v>-0.004148405621883029</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3685,7 +3685,7 @@
         <v>14045</v>
       </c>
       <c r="K64" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -46015,7 +46015,7 @@
         <v>43697</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -7270,7 +7270,7 @@
         <v>1817</v>
       </c>
       <c r="K64" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65">
@@ -35260,7 +35260,7 @@
         <v>1648</v>
       </c>
       <c r="K64" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -3685,7 +3685,7 @@
         <v>14045</v>
       </c>
       <c r="K64" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65">
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -24505,7 +24505,7 @@
         <v>2554</v>
       </c>
       <c r="K64" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65">
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -31675,7 +31675,7 @@
         <v>4461</v>
       </c>
       <c r="K64" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65">
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -35260,7 +35260,7 @@
         <v>1648</v>
       </c>
       <c r="K64" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65">
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38845,7 +38845,7 @@
         <v>3620</v>
       </c>
       <c r="K64" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -42430,7 +42430,7 @@
         <v>2918</v>
       </c>
       <c r="K64" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65">
@@ -45988,16 +45988,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>527164</v>
+        <v>541175</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-0.004148405621883029</v>
+        <v>0.02231940456400182</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>
@@ -46015,7 +46015,7 @@
         <v>43697</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65">
@@ -46031,7 +46031,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.1653811717036824</v>
+        <v>-0.1869894211669053</v>
       </c>
       <c r="E65" t="n">
         <v>29</v>

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -46015,7 +46015,7 @@
         <v>43697</v>
       </c>
       <c r="K64" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -13885,7 +13885,7 @@
         <v>241</v>
       </c>
       <c r="K49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
@@ -46015,7 +46015,7 @@
         <v>43697</v>
       </c>
       <c r="K64" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -3685,7 +3685,7 @@
         <v>14045</v>
       </c>
       <c r="K64" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65">
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -31675,7 +31675,7 @@
         <v>4461</v>
       </c>
       <c r="K64" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -45997,7 +45997,7 @@
         <v>0.02231940456400182</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>
@@ -46015,7 +46015,7 @@
         <v>43697</v>
       </c>
       <c r="K64" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3685,7 +3685,7 @@
         <v>14045</v>
       </c>
       <c r="K64" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65">
@@ -46015,7 +46015,7 @@
         <v>43697</v>
       </c>
       <c r="K64" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -3685,7 +3685,7 @@
         <v>14045</v>
       </c>
       <c r="K64" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65">
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28090,7 +28090,7 @@
         <v>178</v>
       </c>
       <c r="K64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38842,10 +38842,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="K64" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -42430,7 +42430,7 @@
         <v>2918</v>
       </c>
       <c r="K64" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65">
@@ -45997,7 +45997,7 @@
         <v>0.02231940456400182</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>
@@ -46015,7 +46015,7 @@
         <v>43697</v>
       </c>
       <c r="K64" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -3676,16 +3676,16 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>6729</v>
+        <v>6501</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.01962293912194389</v>
+        <v>0.01819581627671161</v>
       </c>
       <c r="J64" t="n">
         <v>14045</v>
       </c>
       <c r="K64" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65">
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.6412150008901331</v>
+        <v>-0.6407121209326916</v>
       </c>
       <c r="J65" t="n">
         <v>10120</v>
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -45997,7 +45997,7 @@
         <v>0.02231940456400182</v>
       </c>
       <c r="E64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>
@@ -46015,7 +46015,7 @@
         <v>43697</v>
       </c>
       <c r="K64" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroPPR.xlsx
+++ b/regionais/registroPPR.xlsx
@@ -3667,7 +3667,7 @@
         <v>0.0614721139239911</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>156168</v>
@@ -7252,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>37421</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>35588</v>
@@ -28072,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>52024</v>
@@ -31675,7 +31675,7 @@
         <v>4461</v>
       </c>
       <c r="K64" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65">
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>30655</v>
@@ -38827,7 +38827,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42412,7 +42412,7 @@
         <v>0.002124510646424138</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>47895</v>
@@ -45997,7 +45997,7 @@
         <v>0.02231940456400182</v>
       </c>
       <c r="E64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>390533</v>
@@ -46015,7 +46015,7 @@
         <v>43697</v>
       </c>
       <c r="K64" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65">
